--- a/design/templates/generated/_climate/CLIMATE_WES_V1_upload_template.xlsx
+++ b/design/templates/generated/_climate/CLIMATE_WES_V1_upload_template.xlsx
@@ -632,27 +632,27 @@
     <row r="3" ht="58" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>do not edit</t>
+          <t>pre-filled - change only to correct an error; the importer checks it</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>do not edit</t>
+          <t>pre-filled - change only to correct an error; the importer checks it</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>do not edit</t>
+          <t>pre-filled - change only to correct an error; the importer checks it</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>do not edit</t>
+          <t>pre-filled - change only to correct an error; the importer checks it</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>do not edit</t>
+          <t>pre-filled - change only to correct an error; the importer checks it</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -2337,7 +2337,6 @@
       <c r="T44" s="8" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:T1"/>
   </mergeCells>
@@ -2488,27 +2487,27 @@
     <row r="3" ht="58" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>do not edit</t>
+          <t>pre-filled - change only to correct an error; the importer checks it</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>do not edit</t>
+          <t>pre-filled - change only to correct an error; the importer checks it</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>do not edit</t>
+          <t>pre-filled - change only to correct an error; the importer checks it</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>do not edit</t>
+          <t>pre-filled - change only to correct an error; the importer checks it</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>do not edit</t>
+          <t>pre-filled - change only to correct an error; the importer checks it</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -4193,7 +4192,6 @@
       <c r="T44" s="8" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
   <mergeCells count="1">
     <mergeCell ref="A1:T1"/>
   </mergeCells>
@@ -4207,7 +4205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A36"/>
+  <dimension ref="A1:A50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -4223,7 +4221,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Province: Western   |   CLIMATE_WES_V1   |   draft generated 2026-09-06</t>
+          <t>Province: Western   |   CLIMATE_WES_V1   |   draft generated 2026-09-14</t>
         </is>
       </c>
     </row>
@@ -4361,85 +4359,175 @@
     <row r="24">
       <c r="A24" s="9" t="inlineStr">
         <is>
-          <t>WHO CAN IMPORT THIS</t>
+          <t>THIS FILE IS NOT PROTECTED</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Importing this file needs the hazard-data grant (app_user.may_write_hazard_domain).</t>
+          <t>Every cell is editable, including DS_CODE, DS_DIVISION, DISTRICT and the YEAR columns.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>That is deliberate: one climate officer owns these numbers for the whole province, so a</t>
+          <t>That is deliberate - an earlier locked issue left wrong YEAR values in returned files</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>sector officer cannot overwrite them by accident.</t>
+          <t>because nobody could correct them. Please still treat the first five columns as</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>pre-filled and change them only to fix a genuine error.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>OPEN QUESTIONS FOR THE PANEL</t>
-        </is>
-      </c>
+      <c r="A29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>a. DROUGHT_EVENTS_1974_TO_2004 and _2005_TO_2022 are marked 'typical year' here because</t>
+          <t>The checks that matter run at import, not in Excel:</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">   that is how the current Central templates treat them. Every other event-count variable</t>
+          <t xml:space="preserve">  - the column set and its order are checked against this file's hidden _META;</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">   is 'fixed window'. The two split variables may have inherited the wrong rule when the</t>
+          <t xml:space="preserve">    a renamed, reordered, added or deleted column is refused and named.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Central panel split DROUGHT_EVENTS_1974_TO_2022 on 2026-09-03. Please confirm which.</t>
+          <t xml:space="preserve">  - every DS_CODE must be a division of this province, or that row is refused.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>b. Landslide columns appear ONLY in provinces that have landslide profiles</t>
+          <t xml:space="preserve">  - the PERIOD comes from the TAB NAME, not from the YEAR_START/YEAR_END cells.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (Central, Northwestern, Sabaragamuwa, Southern, Uva, Western). Eastern, North Central</t>
+          <t xml:space="preserve">    If the two disagree the tab wins and the importer reports the disagreement.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - nothing loads partially: any error means the file loaded nothing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>WHO CAN IMPORT THIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Importing this file needs the hazard-data grant (app_user.may_write_hazard_domain).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>That is deliberate: one climate officer owns these numbers for the whole province, so a</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>sector officer cannot overwrite them by accident.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>OPEN QUESTIONS FOR THE PANEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>a. DROUGHT_EVENTS_1974_TO_2004 and _2005_TO_2022 are marked 'typical year' here because</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   that is how the current Central templates treat them. Every other event-count variable</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   is 'fixed window'. The two split variables may have inherited the wrong rule when the</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Central panel split DROUGHT_EVENTS_1974_TO_2022 on 2026-09-03. Please confirm which.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>b. Landslide columns appear ONLY in provinces that have landslide profiles</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   (Central, Northwestern, Sabaragamuwa, Southern, Uva, Western). Eastern, North Central</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t xml:space="preserve">   and Northern get a drought + flood file only. Confirm that matches the panel's view.</t>
         </is>
@@ -4561,7 +4649,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
